--- a/product_upload/packages/29/file.xlsx
+++ b/product_upload/packages/29/file.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,7 +596,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -645,6 +645,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -669,7 +674,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -828,6 +833,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>POTASSIUM CHLORIDE in DEXTROSE and SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-4BDC1E62C907</t>
         </is>
       </c>
@@ -851,7 +861,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1014,6 +1024,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>POTASSIUM CHLORIDE in DEXTROSE and SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-BF8A1A548F2C</t>
         </is>
       </c>
@@ -1037,7 +1052,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1212,6 +1227,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>ESBRIET 267 mg HARD CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-D7E9DEDA999C</t>
         </is>
       </c>
@@ -1235,7 +1255,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1410,6 +1430,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>OZAPIN 5 mg orally disintegrating tablet</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-7DB4A45F1D0E</t>
         </is>
       </c>
@@ -1433,7 +1458,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1604,6 +1629,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>OZAPIN 10 mg orally disintegrating tablet</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-7A820C111053</t>
         </is>
       </c>
@@ -1627,7 +1657,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1790,6 +1820,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>TAVFLOX 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-2DA4EB65EBC1</t>
         </is>
       </c>
@@ -1813,7 +1848,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1976,6 +2011,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>QUETAL 50 mg XR extended-release tablet</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-4D58052E8337</t>
         </is>
       </c>
@@ -1999,7 +2039,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2166,6 +2206,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>MIDIXIME 100MG\5ML</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-E9FCB39A6314</t>
         </is>
       </c>
@@ -2189,7 +2234,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2352,6 +2397,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>VENCLEXTA 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-A0473AFF9993</t>
         </is>
       </c>
@@ -2375,7 +2425,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2546,6 +2596,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>LAVIE ORAL SOLUTION 150 ML</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-1FA8FBDD97B2</t>
         </is>
       </c>
@@ -2569,7 +2624,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2740,6 +2795,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>ROZAVI 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-055FB27F5FDC</t>
         </is>
       </c>
@@ -2763,7 +2823,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2938,6 +2998,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>ROZAVI 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-8BBA46F42E25</t>
         </is>
       </c>
@@ -2961,7 +3026,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3140,6 +3205,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>DOROFEN 500-50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-44A9787EF445</t>
         </is>
       </c>
@@ -3163,7 +3233,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3338,6 +3408,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>ESSENTIAL D-3 5000 IU CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-54A5463004C8</t>
         </is>
       </c>
@@ -3361,7 +3436,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3536,6 +3611,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>ESSENTIAL D-3 10000 IU CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-3997AAE49D10</t>
         </is>
       </c>
@@ -3559,7 +3639,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3722,6 +3802,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>VENCLEXTA 10 mg / 50 mg / 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-B1E0094AD27D</t>
         </is>
       </c>
@@ -3745,7 +3830,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3920,6 +4005,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>TIMOLOL 0.5% OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-9E2DEDB3B871</t>
         </is>
       </c>
@@ -3943,7 +4033,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4106,6 +4196,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>VIMPAT 10 mg/ml SYRUP</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-C965044CD952</t>
         </is>
       </c>
@@ -4129,7 +4224,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4304,6 +4399,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>NUROFEN 400 DOUBLE STRENGTH TABLET</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-07B2140E4E58</t>
         </is>
       </c>
@@ -4327,7 +4427,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4498,6 +4598,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>EFRAM XR 500 mg TABLET</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-5A07AE70C79D</t>
         </is>
       </c>
@@ -4521,7 +4626,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4696,6 +4801,11 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>EFRAM XR 750 mg TABLET</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-A04B43C47EBE</t>
         </is>
       </c>
@@ -4719,7 +4829,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4894,6 +5004,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>LEVETAM XR 500 mg TABLET</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-2D132E390733</t>
         </is>
       </c>
@@ -4917,7 +5032,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5080,6 +5195,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>ORFADIN 2 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-86E911A7067A</t>
         </is>
       </c>
@@ -5103,7 +5223,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5266,6 +5386,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>ORFADIN 5 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-6F2FF4BE49E5</t>
         </is>
       </c>
@@ -5289,7 +5414,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5456,6 +5581,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>ORFADIN 10 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-5FD2E1CE75EC</t>
         </is>
       </c>
@@ -5479,7 +5609,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5646,6 +5776,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>ORFADIN 20 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-310C0335941C</t>
         </is>
       </c>
@@ -5669,7 +5804,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5840,6 +5975,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>0.18% SODIUM CHLORIDE and 5% DEXTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-CBD37B6E5FF2</t>
         </is>
       </c>
@@ -5863,7 +6003,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6038,6 +6178,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>VULGA 80 mg XR film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-A8E4967B887F</t>
         </is>
       </c>
@@ -6061,7 +6206,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6236,6 +6381,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>VULGA 105 mg XR film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-6B0A09BC5F4F</t>
         </is>
       </c>
@@ -6259,7 +6409,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6430,6 +6580,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>KEPPRA 1000MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-83EB9CA58714</t>
         </is>
       </c>
@@ -6453,7 +6608,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6628,6 +6783,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>KEPPRA 100MG-ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-7388029F0F5D</t>
         </is>
       </c>
@@ -6651,7 +6811,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6822,6 +6982,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>CANESTEN VAGINAL TAB 100MG</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-357469AD5809</t>
         </is>
       </c>
@@ -6845,7 +7010,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -7024,6 +7189,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>MYLERAN</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-D8C459696ACF</t>
         </is>
       </c>
@@ -7047,7 +7217,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7214,6 +7384,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>OXYCONTIN 10 mg controlled release tablet</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-9268851E7EBC</t>
         </is>
       </c>
@@ -7237,7 +7412,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7404,6 +7579,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>CENTRUM SILVER TABLETS</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-6E1F714B6252</t>
         </is>
       </c>
@@ -7427,7 +7607,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7602,6 +7782,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>CENTRUM SILVER TABLETS</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-D7E62D7F0A37</t>
         </is>
       </c>
@@ -7625,7 +7810,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7800,6 +7985,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>CENTRUM WITH LUTEIN TABLETS</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-0F96B730F915</t>
         </is>
       </c>
@@ -7823,7 +8013,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7990,6 +8180,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>CENTRUM WITH LUTEIN TABLETS</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-B412BBFC4CE5</t>
         </is>
       </c>
@@ -8013,7 +8208,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8184,6 +8379,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>MIRTAZA 30 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-13E0BA402F48</t>
         </is>
       </c>
@@ -8207,7 +8407,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8374,6 +8574,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>MIRTAZA 15 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-7351F214BD96</t>
         </is>
       </c>
@@ -8397,7 +8602,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8564,6 +8769,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>CAPRELSA 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-F901100D143F</t>
         </is>
       </c>
@@ -8587,7 +8797,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8754,6 +8964,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>CAPRELSA 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-592078FDB81D</t>
         </is>
       </c>
@@ -8777,7 +8992,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8948,6 +9163,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>MOVICOL SACHET POWDER FOR RECONSTITUTION</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-6A2B407E7E06</t>
         </is>
       </c>
@@ -8971,7 +9191,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9146,6 +9366,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>TELFAST 180 MG FILM COATED TAB</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-3887F621329C</t>
         </is>
       </c>
@@ -9169,7 +9394,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9336,6 +9561,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>TIMOPTOL .DROPS</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-AB9A2BF07781</t>
         </is>
       </c>
@@ -9359,7 +9589,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9526,6 +9756,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>TIMOPTOL .DROPS</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-9BF26D71CD3D</t>
         </is>
       </c>
@@ -9549,7 +9784,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9720,6 +9955,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>BENZAFLEX 5 mg Film-Coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-61C48321A7D8</t>
         </is>
       </c>
@@ -9743,7 +9983,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9914,6 +10154,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>BENZAFLEX 10 mg Film-Coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-A759968FF018</t>
         </is>
       </c>
@@ -9937,7 +10182,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -10108,6 +10353,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>LEVANIX 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-9477B942109A</t>
         </is>
       </c>
@@ -10131,7 +10381,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10306,6 +10556,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>KEPPRA 250MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-263130E42014</t>
         </is>
       </c>
@@ -10329,7 +10584,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10504,6 +10759,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>KEPPRA 500MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-061763356232</t>
         </is>
       </c>
@@ -10527,7 +10787,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10698,6 +10958,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>VULGA 55 mg XR film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-A1FBBE65D3EE</t>
         </is>
       </c>
@@ -10721,7 +10986,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10884,6 +11149,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>LEUKAST 4 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-BE94EE06B036</t>
         </is>
       </c>
@@ -10907,7 +11177,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -11074,6 +11344,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>LEUKAST 5 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-F492D4E25343</t>
         </is>
       </c>
@@ -11097,7 +11372,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11276,6 +11551,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>LOTEVAN PLUS 5MG/160MG/12.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-3094E44E80B2</t>
         </is>
       </c>
@@ -11299,7 +11579,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11474,6 +11754,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>LOTEVAN PLUS 5MG/160MG/25MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-DF1ED8486FDD</t>
         </is>
       </c>
@@ -11497,7 +11782,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11676,6 +11961,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>LOTEVAN PLUS10MG/160MG/12.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-A20271215448</t>
         </is>
       </c>
@@ -11699,7 +11989,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11870,6 +12160,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>LOTEVAN PLUS 10MG/160MG/25MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-B81AB414099C</t>
         </is>
       </c>
@@ -11893,7 +12188,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -12072,6 +12367,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>LOTEVAN PLUS 10MG/320MG/25MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-9E3CE0983301</t>
         </is>
       </c>
@@ -12095,7 +12395,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12262,6 +12562,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>RESOLOR 1 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-33D7CA205A5B</t>
         </is>
       </c>
@@ -12285,7 +12590,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12460,6 +12765,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>IRESSA 250 mg film coated tablet</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-4B5667E719A9</t>
         </is>
       </c>
@@ -12483,7 +12793,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12654,6 +12964,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>ZEMPLAR 1 mcg Capsule</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-19FED895AF59</t>
         </is>
       </c>
@@ -12677,7 +12992,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12852,6 +13167,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>ZEMPLAR 2 mcg Capsule</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-10ADD95004CB</t>
         </is>
       </c>
@@ -12875,7 +13195,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -13038,6 +13358,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>OCUDINE 0.15% EYE DROPS SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-0D4B05DCF54D</t>
         </is>
       </c>
@@ -13061,7 +13386,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -13232,6 +13557,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>NEVOTIC 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-F052C9067258</t>
         </is>
       </c>
@@ -13255,7 +13585,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13430,6 +13760,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>ZYLANZA 5 mg Orodispersible Tablet</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-A17E053D940E</t>
         </is>
       </c>
@@ -13453,7 +13788,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13624,6 +13959,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>ZYLANZA 10 mg Orodispersible Tablet</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-BAB0215D27F1</t>
         </is>
       </c>
@@ -13647,7 +13987,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13822,6 +14162,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>ADRENALINE/EPINEPHRINE INJ 1:1000 INJECTION</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-B94763FAC98E</t>
         </is>
       </c>
@@ -13845,7 +14190,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -14020,6 +14365,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>SEFARIX 125mg/5ml Powder For Suspension</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-DB0AC936EA74</t>
         </is>
       </c>
@@ -14043,7 +14393,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -14222,6 +14572,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>SEFARIX 125mg/5ml Powder For Suspension</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-EAAE69615F3C</t>
         </is>
       </c>
@@ -14245,7 +14600,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14408,6 +14763,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>RESOLOR 2 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-522599EE58E1</t>
         </is>
       </c>
@@ -14431,7 +14791,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14610,6 +14970,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>SAXENDA 6 mg/ml sloution for injection in pre-filled pen</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-3C76041C7C88</t>
         </is>
       </c>
@@ -14633,7 +14998,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14796,6 +15161,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>CLOVAINE 10% w/wgel</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-E6ABB3D9BC2F</t>
         </is>
       </c>
@@ -14819,7 +15189,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14990,6 +15360,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>TENORYL 5 MG film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-7573DAD8CDDA</t>
         </is>
       </c>
@@ -15013,7 +15388,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -15184,6 +15559,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>TENORYL 10 MG film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-287648FDF9EB</t>
         </is>
       </c>
@@ -15207,7 +15587,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15378,6 +15758,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>TRIUMEQ 50mg/600mg/300mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-4BF277D78AE0</t>
         </is>
       </c>
@@ -15401,7 +15786,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15568,6 +15953,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>AERRANE LIQUID FOR INHALATION</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-87755748961E</t>
         </is>
       </c>
@@ -15591,7 +15981,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15758,6 +16148,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>D-CURA 2500 IU oral ampule</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-307F8C492DD9</t>
         </is>
       </c>
@@ -15781,7 +16176,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15948,6 +16343,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>VOTRIENT</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-E6AF363CF7B3</t>
         </is>
       </c>
@@ -15971,7 +16371,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -16138,6 +16538,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>VOTRIENT</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-CECEB6D6D4DD</t>
         </is>
       </c>
@@ -16161,7 +16566,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16340,6 +16745,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>ZOFRAN 4 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-EECCBC793B3F</t>
         </is>
       </c>
@@ -16363,7 +16773,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16534,6 +16944,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>ZOFRAN</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-EADAF5E59C60</t>
         </is>
       </c>
@@ -16557,7 +16972,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16728,6 +17143,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>ZOFRAN MELT 4MG ORAL LYOPHILISATE TABLET</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-A28AE0A0475B</t>
         </is>
       </c>
@@ -16751,7 +17171,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16922,6 +17342,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>ZOFRAN MELT 8MG ORAL LYOPHILISATE TABLET</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-D48199C0D09B</t>
         </is>
       </c>
@@ -16945,7 +17370,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -17120,6 +17545,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>BRINTELLIX 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-E08009C28A8D</t>
         </is>
       </c>
@@ -17143,7 +17573,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -17318,6 +17748,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>BRINTELLIX 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-17615A72EF25</t>
         </is>
       </c>
@@ -17341,7 +17776,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17504,6 +17939,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>INVOKANA 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-F4BC8D6F66D5</t>
         </is>
       </c>
@@ -17527,7 +17967,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17702,6 +18142,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>GLUCARE 1000 mg XR Tablet</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-F9D205FBBACA</t>
         </is>
       </c>
@@ -17725,7 +18170,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17888,6 +18333,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>LEVONIC 250 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-50A99A5046BD</t>
         </is>
       </c>
@@ -17911,7 +18361,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -18086,6 +18536,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>LEVON 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-9096FF81BDE1</t>
         </is>
       </c>
@@ -18109,7 +18564,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -18272,6 +18727,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>LEVON 750 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-5D2FE967E5FE</t>
         </is>
       </c>
@@ -18295,7 +18755,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18466,6 +18926,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>OLENZA 5 mg orally disintegrating tablet</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-964715FF1F4E</t>
         </is>
       </c>
@@ -18489,7 +18954,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18660,6 +19125,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>OLENZA 10 mg orally disintegrating tablet</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-9BC9CFFDDA25</t>
         </is>
       </c>
@@ -18683,7 +19153,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18858,6 +19328,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>OLENZA 15 mg orally disintegrating tablet</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-A0C91EEC5FFC</t>
         </is>
       </c>
@@ -18881,7 +19356,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -19040,6 +19515,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>LEVONIC 750 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-7CAF96719A31</t>
         </is>
       </c>
@@ -19063,7 +19543,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -19226,6 +19706,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>0.3% POTASSIUM CHLORIDE in 5% DEXTROSE Injection USP</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-133091B02AB1</t>
         </is>
       </c>
@@ -19249,7 +19734,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19416,6 +19901,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>0.3% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE USP</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-02E32DFB6BE9</t>
         </is>
       </c>
@@ -19439,7 +19929,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19606,6 +20096,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>0.3% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE USP</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-1E9527E852DA</t>
         </is>
       </c>
@@ -19633,7 +20128,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19800,6 +20295,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>0.075% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-1617C34B157D</t>
         </is>
       </c>
@@ -19827,7 +20327,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19993,6 +20493,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>0.075% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-003533A7C026</t>
         </is>
@@ -20009,7 +20514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20055,100 +20560,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -20180,7 +20690,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -20195,92 +20705,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-11911</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>26.41</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>219</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20312,7 +20827,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -20327,92 +20842,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-74463</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>372.83</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>220</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20444,7 +20964,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20459,92 +20979,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-64213</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>17.3</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>221</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20576,7 +21101,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20591,92 +21116,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-85005</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>65.84</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>222</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20708,7 +21238,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20723,92 +21253,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-21372</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>225.5</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>223</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20840,7 +21375,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20855,92 +21390,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-19047</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>223.45</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>224</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20972,7 +21512,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20987,92 +21527,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-84462</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>126.56</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>225</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21104,7 +21649,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -21119,92 +21664,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-36206</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>205.91</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>226</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21236,7 +21786,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -21251,92 +21801,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-27915</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>52.44</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>227</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21368,7 +21923,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -21383,92 +21938,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-84368</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>280.96</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>228</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21500,7 +22060,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21515,92 +22075,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-48344</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>277.2</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>229</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21617,7 +22182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21723,6 +22288,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21758,7 +22333,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21823,6 +22398,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-156B124F7D8B</t>
         </is>
@@ -21859,7 +22444,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21924,6 +22509,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-507496616586</t>
         </is>
@@ -21960,7 +22555,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -22025,6 +22620,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-D39D5B3B08BB</t>
         </is>
@@ -22061,7 +22666,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -22126,6 +22731,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-9C6823FEF88A</t>
         </is>
@@ -22162,7 +22777,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -22227,6 +22842,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-6DD5FDAE4CA4</t>
         </is>
@@ -22263,7 +22888,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22328,6 +22953,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-ACDD38AF8367</t>
         </is>
@@ -22364,7 +22999,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22429,6 +23064,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-E456C30B4094</t>
         </is>
@@ -22465,7 +23110,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22530,6 +23175,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-2F814EB409C8</t>
         </is>
@@ -22566,7 +23221,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22631,6 +23286,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-9B015F23CC9B</t>
         </is>
@@ -22667,7 +23332,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22732,6 +23397,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-FA444757DDFC</t>
         </is>
@@ -22768,7 +23443,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22833,6 +23508,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-8AFA8F26E8F4</t>
         </is>
@@ -22869,7 +23554,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22934,6 +23619,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-E2F9D4BC314E</t>
         </is>
@@ -22970,7 +23665,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -23035,6 +23730,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-CE7E9AE66EDB</t>
         </is>
@@ -23071,7 +23776,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -23136,6 +23841,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-388B7731CD27</t>
         </is>
@@ -23172,7 +23887,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -23237,6 +23952,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-A0DF217A1D8B</t>
         </is>
@@ -23273,7 +23998,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23338,6 +24063,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-9A272D1D661D</t>
         </is>
@@ -23374,7 +24109,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23439,6 +24174,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-6656B4C28935</t>
         </is>
@@ -23475,7 +24220,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23540,6 +24285,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-A0AFBE25AD10</t>
         </is>
@@ -23576,7 +24331,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23641,6 +24396,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-3228E63A6618</t>
         </is>
@@ -23677,7 +24442,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23742,6 +24507,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-CF27C9193BAF</t>
         </is>

--- a/product_upload/packages/29/file.xlsx
+++ b/product_upload/packages/29/file.xlsx
@@ -682,8 +682,16 @@
           <t>5688703979-697-824066944909</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ POTASSIUM CHLORIDE in DEXTROSE and SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>POTASSIUM CHLORIDE in DEXTROSE and SODIUM CHLORIDE Injection USP detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
@@ -869,8 +877,16 @@
           <t>7217340654-504-699661844969</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ POTASSIUM CHLORIDE in DEXTROSE and SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>POTASSIUM CHLORIDE in DEXTROSE and SODIUM CHLORIDE Injection USP detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1665,8 +1681,16 @@
           <t>1469786412-512-520958447404</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TAVFLOX 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TAVFLOX 500 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1856,8 +1880,16 @@
           <t>0585189538-824-265593297894</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUETAL 50 mg XR extended-release tablet</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>QUETAL 50 mg XR extended-release tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
@@ -2047,8 +2079,16 @@
           <t>1802549224-668-506955708395</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MIDIXIME 100MG\5ML</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>MIDIXIME 100MG\5ML detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -2242,8 +2282,16 @@
           <t>7988569988-953-598883724558</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VENCLEXTA 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>VENCLEXTA 100 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
@@ -3647,8 +3695,16 @@
           <t>1334073251-974-183803481473</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VENCLEXTA 10 mg / 50 mg / 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>VENCLEXTA 10 mg / 50 mg / 100 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
@@ -4041,8 +4097,16 @@
           <t>2138975454-163-340864033296</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIMPAT 10 mg/ml SYRUP</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>VIMPAT 10 mg/ml SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
@@ -5040,8 +5104,16 @@
           <t>7112434821-534-685501101189</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ORFADIN 2 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ORFADIN 2 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
@@ -5231,8 +5303,16 @@
           <t>8778215045-470-886755287565</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ORFADIN 5 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ORFADIN 5 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
@@ -5422,8 +5502,16 @@
           <t>2688034167-184-231213354846</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ORFADIN 10 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ORFADIN 10 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
@@ -5617,8 +5705,16 @@
           <t>8579266580-942-343917385019</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ORFADIN 20 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ORFADIN 20 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
@@ -5812,8 +5908,16 @@
           <t>6770678520-105-419277186896</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.18% SODIUM CHLORIDE and 5% DEXTROSE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.18% SODIUM CHLORIDE and 5% DEXTROSE intravenous infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>0</t>
@@ -7225,8 +7329,16 @@
           <t>8754637196-179-547524654180</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OXYCONTIN 10 mg controlled release tablet</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>OXYCONTIN 10 mg controlled release tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>0</t>
@@ -8610,8 +8722,16 @@
           <t>1046730481-216-115706039657</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CAPRELSA 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>CAPRELSA 100 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>0</t>
@@ -8805,8 +8925,16 @@
           <t>2836451965-943-108746256008</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CAPRELSA 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>CAPRELSA 300 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>0</t>
@@ -9402,8 +9530,16 @@
           <t>7454368029-218-200199783326</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TIMOPTOL .DROPS</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>TIMOPTOL .DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>0</t>
@@ -9597,8 +9733,16 @@
           <t>4273736725-792-204170413270</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TIMOPTOL .DROPS</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>TIMOPTOL .DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>0</t>
@@ -10190,8 +10334,16 @@
           <t>6438986755-856-331760682658</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVANIX 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>LEVANIX 500 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>0</t>
@@ -10994,8 +11146,16 @@
           <t>8330439984-851-507829627985</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEUKAST 4 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>LEUKAST 4 mg chewable tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>0</t>
@@ -11185,8 +11345,16 @@
           <t>9408842321-352-475828844748</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEUKAST 5 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>LEUKAST 5 mg chewable tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>0</t>
@@ -12403,8 +12571,16 @@
           <t>8205747531-500-435375591370</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RESOLOR 1 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>RESOLOR 1 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>0</t>
@@ -13203,8 +13379,16 @@
           <t>8323715363-178-435561469160</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OCUDINE 0.15% EYE DROPS SOLUTION</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>OCUDINE 0.15% EYE DROPS SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13394,8 +13578,16 @@
           <t>4090153517-460-157401158885</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEVOTIC 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>NEVOTIC 500 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>0</t>
@@ -13593,8 +13785,16 @@
           <t>0134158970-331-471140186321</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYLANZA 5 mg Orodispersible Tablet</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ZYLANZA 5 mg Orodispersible Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>0</t>
@@ -13796,8 +13996,16 @@
           <t>5167357450-323-723206997151</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYLANZA 10 mg Orodispersible Tablet</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ZYLANZA 10 mg Orodispersible Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>0</t>
@@ -14608,8 +14816,16 @@
           <t>2014927283-952-230810175552</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RESOLOR 2 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>RESOLOR 2 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>0</t>
@@ -15006,8 +15222,16 @@
           <t>7858389789-527-547319009094</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLOVAINE 10% w/wgel</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>CLOVAINE 10% w/wgel detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>0</t>
@@ -15595,8 +15819,16 @@
           <t>9267856896-274-160756801420</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRIUMEQ 50mg/600mg/300mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>TRIUMEQ 50mg/600mg/300mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>0</t>
@@ -15794,8 +16026,16 @@
           <t>3961354794-103-729013915317</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AERRANE LIQUID FOR INHALATION</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>AERRANE LIQUID FOR INHALATION detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>0</t>
@@ -16781,8 +17021,16 @@
           <t>3644803436-991-563361437346</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZOFRAN</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ZOFRAN detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>0</t>
@@ -16980,8 +17228,16 @@
           <t>9257803693-996-807428654460</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZOFRAN MELT 4MG ORAL LYOPHILISATE TABLET</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ZOFRAN MELT 4MG ORAL LYOPHILISATE TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>0</t>
@@ -17179,8 +17435,16 @@
           <t>0268927217-662-843100762507</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZOFRAN MELT 8MG ORAL LYOPHILISATE TABLET</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ZOFRAN MELT 8MG ORAL LYOPHILISATE TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>0</t>
@@ -17784,8 +18048,16 @@
           <t>0971350573-308-303179819665</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ INVOKANA 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>INVOKANA 300 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>0</t>
@@ -18178,8 +18450,16 @@
           <t>1562915463-318-578055999573</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVONIC 250 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>LEVONIC 250 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>0</t>
@@ -18572,8 +18852,16 @@
           <t>5065897005-813-436756776709</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVON 750 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>LEVON 750 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>0</t>
@@ -19364,8 +19652,16 @@
           <t>8619381843-185-035833707272</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVONIC 750 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>LEVONIC 750 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>0</t>
@@ -19551,8 +19847,16 @@
           <t>1435216679-663-885473620583</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.3% POTASSIUM CHLORIDE in 5% DEXTROSE Injection USP</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>0.3% POTASSIUM CHLORIDE in 5% DEXTROSE Injection USP detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>0</t>
@@ -19742,8 +20046,16 @@
           <t>6618619656-649-576064681862</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.3% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE USP</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>0.3% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE USP detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>0</t>
@@ -19937,8 +20249,16 @@
           <t>1589195418-550-062369324806</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.3% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE USP</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>0.3% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE USP detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
           <t>0</t>
@@ -20136,8 +20456,16 @@
           <t>4230309037-780-685287178633</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.075% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>0.075% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>0</t>
@@ -20335,8 +20663,16 @@
           <t>3480290183-492-098265941517</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.075% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>0.075% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>0</t>

--- a/product_upload/packages/29/file.xlsx
+++ b/product_upload/packages/29/file.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20896,7 +20896,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22518,7 +22518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22599,40 +22599,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22712,38 +22717,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>201.29</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-156B124F7D8B</t>
         </is>
@@ -22823,38 +22833,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>462.94</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-507496616586</t>
         </is>
@@ -22934,38 +22949,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>67.67</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-D39D5B3B08BB</t>
         </is>
@@ -23045,38 +23065,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>119.36</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-9C6823FEF88A</t>
         </is>
@@ -23156,38 +23181,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>437.27</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-6DD5FDAE4CA4</t>
         </is>
@@ -23267,38 +23297,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>134.73</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-ACDD38AF8367</t>
         </is>
@@ -23378,38 +23413,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>144.02</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-E456C30B4094</t>
         </is>
@@ -23489,38 +23529,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>175.48</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-2F814EB409C8</t>
         </is>
@@ -23600,38 +23645,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>423.61</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-9B015F23CC9B</t>
         </is>
@@ -23711,38 +23761,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>269.7</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-FA444757DDFC</t>
         </is>
@@ -23822,38 +23877,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>147.92</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-8AFA8F26E8F4</t>
         </is>
@@ -23933,38 +23993,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>374.56</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-E2F9D4BC314E</t>
         </is>
@@ -24044,38 +24109,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>61.59</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-CE7E9AE66EDB</t>
         </is>
@@ -24155,38 +24225,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>32.7</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-388B7731CD27</t>
         </is>
@@ -24266,38 +24341,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>414.57</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-A0DF217A1D8B</t>
         </is>
@@ -24377,38 +24457,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>331.71</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-9A272D1D661D</t>
         </is>
@@ -24488,38 +24573,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>84.38</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-6656B4C28935</t>
         </is>
@@ -24599,38 +24689,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>307.25</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-A0AFBE25AD10</t>
         </is>
@@ -24710,38 +24805,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>205.93</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-3228E63A6618</t>
         </is>
@@ -24821,38 +24921,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>156.34</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-CF27C9193BAF</t>
         </is>
